--- a/estimates/vas2686-parkade/estimate-internal.xlsx
+++ b/estimates/vas2686-parkade/estimate-internal.xlsx
@@ -72,7 +72,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -85,11 +85,16 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00555555"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,7 +108,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -716,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -728,7 +741,8 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -816,10 +830,15 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -840,6 +859,7 @@
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -872,12 +892,15 @@
       <c r="H10" s="12" t="n">
         <v>1625.36</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="13" t="n">
+        <v>14275.36</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>A-1.0 / A-2.1</t>
         </is>
@@ -897,19 +920,22 @@
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>A-1.0 title block</t>
         </is>
@@ -929,19 +955,22 @@
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>A-6.0 / A-6.1</t>
         </is>
@@ -961,19 +990,22 @@
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>A-1.0</t>
         </is>
@@ -993,19 +1025,22 @@
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G14" s="11" t="n"/>
       <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>A-6.0 / A-6.1</t>
         </is>
@@ -1025,19 +1060,22 @@
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1057,19 +1095,22 @@
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>BY OWNER</t>
         </is>
       </c>
       <c r="G16" s="11" t="n"/>
       <c r="H16" s="11" t="n"/>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1089,19 +1130,22 @@
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>NOT INCLUDED</t>
         </is>
       </c>
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>A-1.0 code summary</t>
         </is>
@@ -1138,12 +1182,15 @@
       <c r="H18" s="12" t="n">
         <v>591.04</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="13" t="n">
+        <v>13174.24</v>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>A-1.0</t>
         </is>
@@ -1180,12 +1227,15 @@
       <c r="H19" s="12" t="n">
         <v>295.52</v>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="13" t="n">
+        <v>12172.52</v>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>A-1.0</t>
         </is>
@@ -1222,12 +1272,15 @@
       <c r="H20" s="12" t="n">
         <v>295.52</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="13" t="n">
+        <v>7115.52</v>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>A-1.0</t>
         </is>
@@ -1264,12 +1317,15 @@
       <c r="H21" s="12" t="n">
         <v>147.76</v>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="13" t="n">
+        <v>2715.76</v>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>P.C. allowance</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>A-2.1</t>
         </is>
@@ -1302,12 +1358,15 @@
       </c>
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="11" t="n"/>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="13" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>Quote</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1344,12 +1403,15 @@
       <c r="H23" s="12" t="n">
         <v>2142.52</v>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="13" t="n">
+        <v>21098.52</v>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>A-1.0 scope of work</t>
         </is>
@@ -1386,173 +1448,119 @@
       <c r="H24" s="12" t="n">
         <v>38122.07999999999</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="13" t="n">
+        <v>38122.07999999999</v>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 1 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="18" t="n">
+        <v>74954.2</v>
+      </c>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="18" t="n">
+        <v>43219.8</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <v>118174</v>
+      </c>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>DIVISION 2 - SITEWORK</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Hazardous materials survey and abatement — building constructed 1990; no survey provided</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
-        </is>
-      </c>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>A-1.0 code summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>New trees, shrubs and planting — NO LANDSCAPE DRAWINGS IN THIS SET; A-6.0 refers to landscape for all finishes. P.C.</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>P.C.</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>A-2.1 / A-6.0</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Topsoil and lawn — reinstate lawn areas over deck</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>9590</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+          <t>Hazardous materials survey and abatement — building constructed 1990; no survey provided</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>A-1.0 / A-2.1</t>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 code summary</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Subsurface drainage — drain rock, 8" perforated PVC pipe at bottom, filter fabric to drain sumps</t>
+          <t>New trees, shrubs and planting — NO LANDSCAPE DRAWINGS IN THIS SET; A-6.0 refers to landscape for all finishes. P.C.</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>320</v>
+        <v>1</v>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>lineal</t>
+          <t>P.C.</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>34</v>
+        <v>18000</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>10880</v>
+        <v>18000</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>2</v>
@@ -1560,694 +1568,689 @@
       <c r="H29" s="12" t="n">
         <v>147.76</v>
       </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+      <c r="I29" s="13" t="n">
+        <v>18147.76</v>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>A-6.1 details 02, 03</t>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1 / A-6.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Freestanding landscape wall / fence replaced per A-6.0 detail 06; reuse two existing gates</t>
+          <t>Topsoil and lawn — reinstate lawn areas over deck</t>
         </is>
       </c>
       <c r="C30" s="11" t="n">
-        <v>80</v>
+        <v>1400</v>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>lineal</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>90.23999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>7219.2</v>
+        <v>9590</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
+        <v>73.88</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>9663.879999999999</v>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 06 / A-2.1</t>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 / A-2.1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Reconstruction of the concrete driveway ramp surface — outside the slab remediation scope line shown on A-2.1</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
+          <t>Subsurface drainage — drain rock, 8" perforated PVC pipe at bottom, filter fabric to drain sumps</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>320</v>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>lineal</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>10880</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>11027.76</v>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 details 02, 03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Hard landscaping — BBQ area, steps and miscellaneous hardscape per landscape drawings not issued. P.C.</t>
+          <t>Freestanding landscape wall / fence replaced per A-6.0 detail 06; reuse two existing gates</t>
         </is>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>P.C.</t>
+          <t>lineal</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>12000</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>12000</v>
+        <v>7219.2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
+        <v>295.52</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>7514.719999999999</v>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 06 / A-2.1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Demolition — remove existing concrete topping and path paving over the parkade deck to expose top of structural slab. Saw-cut and break out over a live membrane and occupied parkade</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>14280</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>283</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>20908.04</v>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
+          <t>Reconstruction of the concrete driveway ramp surface — outside the slab remediation scope line shown on A-2.1</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>A-1.0 scope / A-2.1</t>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Excavation — remove fill and gravel over deck; strip grade on east side of 1988 Ogden and at edges of common paths to expose top of parkade wall. Hand excavation within TPZs</t>
+          <t>Hard landscaping — BBQ area, steps and miscellaneous hardscape per landscape drawings not issued. P.C.</t>
         </is>
       </c>
       <c r="C34" s="11" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>cubic yards</t>
+          <t>P.C.</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>24</v>
+        <v>12000</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>7683.52</v>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
+        <v>147.76</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>12147.76</v>
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>A-1.0 scope / A-6.0 details 02, 03</t>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Remove section of hedge #9 to enable installation of scaffolding; protect and retain all balance of trees, hedges and shrubs</t>
+          <t>Demolition — remove existing concrete topping and path paving over the parkade deck to expose top of structural slab. Saw-cut and break out over a live membrane and occupied parkade</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1</v>
+        <v>3400</v>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>3200</v>
+        <v>4.2</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3200</v>
+        <v>14280</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>8</v>
+        <v>283</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>591.04</v>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+        <v>20908.04</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>35188.03999999999</v>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>A-1.0</t>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 scope / A-2.1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Street cleaning and washing — Ogden Ave, Maple St and lane, over the programme</t>
+          <t>Excavation — remove fill and gravel over deck; strip grade on east side of 1988 Ogden and at edges of common paths to expose top of parkade wall. Hand excavation within TPZs</t>
         </is>
       </c>
       <c r="C36" s="11" t="n">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>cubic yards</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>2640</v>
+        <v>3000</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>812.6799999999999</v>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
+        <v>7683.52</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>10683.52</v>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>A-1.0</t>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 scope / A-6.0 details 02, 03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Pea gravel bedding — 5/8" to 3/8", no organics, ASTM C-33, to paver areas and drainage</t>
+          <t>Remove section of hedge #9 to enable installation of scaffolding; protect and retain all balance of trees, hedges and shrubs</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>sq.ft.</t>
+          <t>at</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.41</v>
+        <v>3200</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2820</v>
+        <v>3200</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3250.72</v>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
+        <v>591.04</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>3791.04</v>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 material list</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>New concrete pavers on pea gravel — common paths and patios</t>
+          <t>Street cleaning and washing — Ogden Ave, Maple St and lane, over the programme</t>
         </is>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1400</v>
+        <v>11</v>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>sq.ft.</t>
+          <t>months</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>17.12</v>
+        <v>240</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>23968</v>
+        <v>2640</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+        <v>812.6799999999999</v>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>3452.68</v>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>A-2.1</t>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Pea gravel bedding — 5/8" to 3/8", no organics, ASTM C-33, to paver areas and drainage</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>sq.ft.</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2820</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>3250.72</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>6070.719999999999</v>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 material list</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>New concrete pavers on pedestals — rear patio at 1988 Ogden</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>600</v>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>New concrete pavers on pea gravel — common paths and patios</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>sq.ft.</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>23.54</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>14124</v>
-      </c>
-      <c r="G39" s="11" t="n">
+      <c r="E40" s="12" t="n">
+        <v>17.12</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>23968</v>
+      </c>
+      <c r="G40" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>73.88</v>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I40" s="13" t="n">
+        <v>24041.88</v>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>A-2.1 / A-6.0 detail 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 3 - CONCRETE</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>New 4" ht pre-curb at building perimeters, 4" gap every 4'-0" and at low spots for drainage, 1/2" expansion joint to existing curb</t>
+          <t>New concrete pavers on pedestals — rear patio at 1988 Ogden</t>
         </is>
       </c>
       <c r="C41" s="11" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>lineal</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>40.66</v>
+        <v>23.54</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>12198</v>
+        <v>14124</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
+        <v>73.88</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>14197.88</v>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 01</t>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1 / A-6.0 detail 01</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>New concrete topping sloped 2% to edge / drain over full deck. Drawings note 'CONTRACTOR TO CONFIRM IF EXISTING IS SLOPED' — priced on an average 2" topping</t>
-        </is>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>34578</v>
-      </c>
-      <c r="G42" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>221.64</v>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 details 01–06</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Reinforcing steel to pre-curb and topping — NO STRUCTURAL DRAWINGS IN THIS SET; A-6.0 and A-6.1 both refer to structural. P.C.</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>P.C.</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 / A-6.1</t>
-        </is>
-      </c>
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 2 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="18" t="n">
+        <v>121721.2</v>
+      </c>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="18" t="n">
+        <v>34206.44</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>155927.64</v>
+      </c>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="16" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>Concrete remediation of exposed slab, curbs and parkade wall — extent cannot be determined until the slab is exposed. P.C. sized at repair to 15% of deck area</t>
-        </is>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>P.C.</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>591.04</v>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>A-1.0 scope of work</t>
-        </is>
-      </c>
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 3 - CONCRETE</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Structural repair to parkade slab, columns, beams or walls beyond surface concrete remediation</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
+          <t>New 4" ht pre-curb at building perimeters, 4" gap every 4'-0" and at low spots for drainage, 1/2" expansion joint to existing curb</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>lineal</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>12198</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>12345.76</v>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>A-1.0 scope of work</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>New concrete curb at exterior stairwell (parking exit at 1988 Ogden) and half-round concrete cap to landscape wall, c/w new reveal and caulking</t>
+          <t>New concrete topping sloped 2% to edge / drain over full deck. Drawings note 'CONTRACTOR TO CONFIRM IF EXISTING IS SLOPED' — priced on an average 2" topping</t>
         </is>
       </c>
       <c r="C46" s="11" t="n">
-        <v>105</v>
+        <v>3400</v>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>lineal</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>52</v>
+        <v>10.17</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>5460</v>
+        <v>34578</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
+        <v>221.64</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>34799.64</v>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>A-6.1 detail 01 / A-6.0 detail 03</t>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 details 01–06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Landscape concrete placement at stairwell curb and caps</t>
+          <t>Reinforcing steel to pre-curb and topping — NO STRUCTURAL DRAWINGS IN THIS SET; A-6.0 and A-6.1 both refer to structural. P.C.</t>
         </is>
       </c>
       <c r="C47" s="11" t="n">
@@ -2255,14 +2258,14 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>P.C.</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>4800</v>
+        <v>9500</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>4800</v>
+        <v>9500</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>2</v>
@@ -2270,88 +2273,113 @@
       <c r="H47" s="12" t="n">
         <v>147.76</v>
       </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+      <c r="I47" s="13" t="n">
+        <v>9647.76</v>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>A-6.1 detail 01</t>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 / A-6.1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 5 - METALS</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
-      <c r="J48" s="10" t="n"/>
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Concrete remediation of exposed slab, curbs and parkade wall — extent cannot be determined until the slab is exposed. P.C. sized at repair to 15% of deck area</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>P.C.</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G48" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>591.04</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>32591.04</v>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 scope of work</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Prefinished metal flashing — Cascadia 20ga, custom colour by architect, c/w 4" upleg, extended to 1/2" of grade</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>lineal</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>11555</v>
-      </c>
-      <c r="G49" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>1847</v>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
+          <t>Structural repair to parkade slab, columns, beams or walls beyond surface concrete remediation</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 material list / details 01, 02</t>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 scope of work</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Perforated aluminum drain strip at base of exterior wall</t>
+          <t>New concrete curb at exterior stairwell (parking exit at 1988 Ogden) and half-round concrete cap to landscape wall, c/w new reveal and caulking</t>
         </is>
       </c>
       <c r="C50" s="11" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
@@ -2359,1049 +2387,1486 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>28.25</v>
+        <v>52</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3248.75</v>
+        <v>5460</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>443.28</v>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
+        <v>147.76</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>5607.76</v>
       </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 detail 01</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 detail 01 / A-6.0 detail 03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Landscape concrete placement at stairwell curb and caps</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>4947.76</v>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 detail 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="n"/>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 3 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="18" t="n">
+        <v>98536</v>
+      </c>
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="18" t="n">
+        <v>1403.72</v>
+      </c>
+      <c r="I52" s="18" t="n">
+        <v>99939.72</v>
+      </c>
+      <c r="J52" s="16" t="n"/>
+      <c r="K52" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 5 - METALS</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Insect screen at drain strip and flashing terminations</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>115</v>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Prefinished metal flashing — Cascadia 20ga, custom colour by architect, c/w 4" upleg, extended to 1/2" of grade</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>lineal</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>736</v>
-      </c>
-      <c r="G51" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="E55" s="12" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>11555</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>1847</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>13402</v>
+      </c>
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>Self-perform</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 details 01, 02</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Reuse existing gates — remove, store, adjust and rehang two gates</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>420</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>840</v>
-      </c>
-      <c r="G52" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>443.28</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Self-perform</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>A-2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>New top-mounted guard, 3'-6" above walking surface, at exterior stairwell / parking exit at 1988 Ogden</t>
-        </is>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>lineal</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="n">
-        <v>372.24</v>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>9306</v>
-      </c>
-      <c r="G53" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>A-6.1 detail 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>New galvanized steel grate to parkade fan vent lid, c/w debris shroud to drain</t>
-        </is>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>1926</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>1926</v>
-      </c>
-      <c r="G54" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Quote</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>A-1.0 / A-2.1 vent note</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 6 - WOOD AND PLASTICS</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 material list / details 01, 02</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Replace deteriorated plywood sheathing and wall studs at base of exterior walls — extent unknown until opened; studs to be reviewed by structural. Includes the 20% renovation uplift on framing labour. P.C.</t>
+          <t>Perforated aluminum drain strip at base of exterior wall</t>
         </is>
       </c>
       <c r="C56" s="11" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>P.C.</t>
+          <t>lineal</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>14000</v>
+        <v>28.25</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>14000</v>
+        <v>3248.75</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>2142.52</v>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
+        <v>443.28</v>
+      </c>
+      <c r="I56" s="13" t="n">
+        <v>3692.03</v>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
           <t>A-6.0 detail 01</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 7 - THERMAL AND MOISTURE PROTECTION</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Insect screen at drain strip and flashing terminations</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>115</v>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>lineal</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>736</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="I57" s="13" t="n">
+        <v>1031.52</v>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 details 01, 02</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>1/2" drain mat and filter fabric (Sopradrain 150 / Ecodrain E or approved alternate) over deck and up walls; new drain mat lapped over existing at cold joints. Includes 10% waste</t>
+          <t>Reuse existing gates — remove, store, adjust and rehang two gates</t>
         </is>
       </c>
       <c r="C58" s="11" t="n">
-        <v>3740</v>
+        <v>2</v>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>sq.ft.</t>
+          <t>at</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>2.38</v>
+        <v>420</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>8901.199999999999</v>
+        <v>840</v>
       </c>
       <c r="G58" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+        <v>443.28</v>
+      </c>
+      <c r="I58" s="13" t="n">
+        <v>1283.28</v>
       </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 all details / material list</t>
+          <t>Self-perform</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
+        <is>
+          <t>A-2.1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>2" concrete-faced insulation at parkade wall head, and 1/2" min insulation around drains</t>
+          <t>New top-mounted guard, 3'-6" above walking surface, at exterior stairwell / parking exit at 1988 Ogden</t>
         </is>
       </c>
       <c r="C59" s="11" t="n">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>sq.ft.</t>
+          <t>lineal</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>8.35</v>
+        <v>372.24</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3340</v>
+        <v>9306</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
+        <v>73.88</v>
+      </c>
+      <c r="I59" s="13" t="n">
+        <v>9379.879999999999</v>
+      </c>
+      <c r="J59" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 02 / A-6.1 details 02, 03</t>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 detail 01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Insulation, vapour barrier, concrete topping, gypsum board and interior finish at base of exterior walls — explicitly noted BY INTERIOR RENO CONTRACTOR</t>
-        </is>
-      </c>
-      <c r="C60" s="11" t="n"/>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
-        </is>
-      </c>
-      <c r="G60" s="11" t="n"/>
-      <c r="H60" s="11" t="n"/>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
+          <t>New galvanized steel grate to parkade fan vent lid, c/w debris shroud to drain</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>1926</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>1926</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="I60" s="13" t="n">
+        <v>2221.52</v>
       </c>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 detail 01</t>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 / A-2.1 vent note</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Blueskin VP100 vapour-permeable self-adhered sheathing membrane at wall bases, lapped over metal flashing and sealed to degranulated cap sheet</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>2700</v>
-      </c>
-      <c r="G61" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 material list / detail 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>6mil polyethylene vapour barrier</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>600</v>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>432</v>
-      </c>
-      <c r="G62" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 material list</t>
-        </is>
-      </c>
+      <c r="A61" s="16" t="n"/>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 5 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="18" t="n">
+        <v>27611.75</v>
+      </c>
+      <c r="G61" s="16" t="n"/>
+      <c r="H61" s="18" t="n">
+        <v>3398.48</v>
+      </c>
+      <c r="I61" s="18" t="n">
+        <v>31010.23</v>
+      </c>
+      <c r="J61" s="16" t="n"/>
+      <c r="K61" s="16" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>Poly root barrier at planted areas</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>1526</v>
-      </c>
-      <c r="G63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>A-6.1 details 02, 03</t>
-        </is>
-      </c>
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 6 - WOOD AND PLASTICS</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>2-ply SBS roofing membrane — complete system with all accessories (Soprema, IKO, Bakor or approved alternate), over deck and upturned to min 8" above finished grade, extended 12" past cold joints. 3,400 sq.ft. deck + 750 sq.ft. upturn, 10% waste</t>
+          <t>Replace deteriorated plywood sheathing and wall studs at base of exterior walls — extent unknown until opened; studs to be reviewed by structural. Includes the 20% renovation uplift on framing labour. P.C.</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
-        <v>4565</v>
+        <v>1</v>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>sq.ft.</t>
+          <t>P.C.</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>22.56</v>
+        <v>14000</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>102986.4</v>
+        <v>14000</v>
       </c>
       <c r="G64" s="11" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>591.04</v>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
+        <v>2142.52</v>
+      </c>
+      <c r="I64" s="13" t="n">
+        <v>16142.52</v>
       </c>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>A-6.0 all details</t>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 01</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>PMMA membrane (Alsan RS 230) terminating SBS on remaining exposed concrete, lapped onto SBS 8" and onto concrete 8"</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>620</v>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>sq.ft.</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>19.26</v>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>11941.2</v>
-      </c>
-      <c r="G65" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J65" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 05 / A-6.1 detail 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>Temporary membrane termination — single-component Alsan flashing night seals at edges of work areas, required for construction sequencing around 1988 Ogden</t>
-        </is>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>400</v>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>lineal</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>9800</v>
-      </c>
-      <c r="G66" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 04</t>
-        </is>
-      </c>
+      <c r="A65" s="16" t="n"/>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 6 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
+      <c r="F65" s="18" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G65" s="16" t="n"/>
+      <c r="H65" s="18" t="n">
+        <v>2142.52</v>
+      </c>
+      <c r="I65" s="18" t="n">
+        <v>16142.52</v>
+      </c>
+      <c r="J65" s="16" t="n"/>
+      <c r="K65" s="16" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>Hot rubber roof membrane lapped into drain sumps, 10"x10"x3/4" recess formed in slab</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>780</v>
-      </c>
-      <c r="F67" s="12" t="n">
-        <v>4680</v>
-      </c>
-      <c r="G67" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>147.76</v>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>Subtrade</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>A-6.1 details 02, 03</t>
-        </is>
-      </c>
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 7 - THERMAL AND MOISTURE PROTECTION</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Seal all slab penetrations</t>
+          <t>1/2" drain mat and filter fabric (Sopradrain 150 / Ecodrain E or approved alternate) over deck and up walls; new drain mat lapped over existing at cold joints. Includes 10% waste</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1</v>
+        <v>3740</v>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>3400</v>
+        <v>2.38</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>3400</v>
+        <v>8901.199999999999</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
+        <v>147.76</v>
+      </c>
+      <c r="I68" s="13" t="n">
+        <v>9048.959999999999</v>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J68" s="11" t="inlineStr">
-        <is>
-          <t>A-6.0 detail 01</t>
+      <c r="K68" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 all details / material list</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 9 - FINISHES</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>2" concrete-faced insulation at parkade wall head, and 1/2" min insulation around drains</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>sq.ft.</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>3340</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I69" s="13" t="n">
+        <v>3487.76</v>
+      </c>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 02 / A-6.1 details 02, 03</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Repair of interior finishes damaged by pre-existing water ingress</t>
+          <t>Insulation, vapour barrier, concrete topping, gypsum board and interior finish at base of exterior walls — explicitly noted BY INTERIOR RENO CONTRACTOR</t>
         </is>
       </c>
       <c r="C70" s="11" t="n"/>
       <c r="D70" s="11" t="n"/>
       <c r="E70" s="11" t="n"/>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>BY OTHERS</t>
         </is>
       </c>
       <c r="G70" s="11" t="n"/>
       <c r="H70" s="11" t="n"/>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="I70" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K70" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 01</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 10 - SPECIALTIES</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Blueskin VP100 vapour-permeable self-adhered sheathing membrane at wall bases, lapped over metal flashing and sealed to degranulated cap sheet</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>sq.ft.</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I71" s="13" t="n">
+        <v>2847.76</v>
+      </c>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 material list / detail 01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>REPURPOSED CODE — Firestopping. New 2hr F/T rated firestopping at parkade ceiling where existing products cannot practically be retained. P.C.</t>
+          <t>6mil polyethylene vapour barrier</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>sq.ft.</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="G72" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I72" s="13" t="n">
+        <v>579.76</v>
+      </c>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 material list</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Poly root barrier at planted areas</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>sq.ft.</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>1526</v>
+      </c>
+      <c r="G73" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>P.C.</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G72" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>591.04</v>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
-      </c>
-      <c r="J72" s="11" t="inlineStr">
-        <is>
-          <t>A-1.0 code summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>DIVISION 15 - MECHANICAL</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
+      <c r="H73" s="12" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="I73" s="13" t="n">
+        <v>1599.88</v>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 details 02, 03</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Bi-level area drains c/w adjustable grate flush with pavers, and deck drains — NO MECHANICAL DRAWINGS IN THIS SET; A-6.1 refers to mech for all drains. Count assumed</t>
+          <t>2-ply SBS roofing membrane — complete system with all accessories (Soprema, IKO, Bakor or approved alternate), over deck and upturned to min 8" above finished grade, extended 12" past cold joints. 3,400 sq.ft. deck + 750 sq.ft. upturn, 10% waste</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
-        <v>6</v>
+        <v>4565</v>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>909.5</v>
+        <v>22.56</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>5457</v>
+        <v>102986.4</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>443.28</v>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
+        <v>591.04</v>
+      </c>
+      <c r="I74" s="13" t="n">
+        <v>103577.44</v>
+      </c>
+      <c r="J74" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>A-6.1 details 02, 03</t>
+      <c r="K74" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 all details</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Tie-in of new deck drains to existing parkade storm drainage — no as-built information available. P.C.</t>
+          <t>PMMA membrane (Alsan RS 230) terminating SBS on remaining exposed concrete, lapped onto SBS 8" and onto concrete 8"</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>1</v>
+        <v>620</v>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>P.C.</t>
+          <t>sq.ft.</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>8500</v>
+        <v>19.26</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>8500</v>
+        <v>11941.2</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>295.52</v>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>P.C. allowance</t>
-        </is>
+        <v>147.76</v>
+      </c>
+      <c r="I75" s="13" t="n">
+        <v>12088.96</v>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>A-6.1</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 05 / A-6.1 detail 01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Sprinkler system modifications — A-1.0 refers to separate sprinkler drawings for 1988 Ogden, not issued</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="n"/>
-      <c r="D76" s="11" t="n"/>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="13" t="inlineStr">
-        <is>
-          <t>NOT INCLUDED</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="n"/>
-      <c r="H76" s="11" t="n"/>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
+          <t>Temporary membrane termination — single-component Alsan flashing night seals at edges of work areas, required for construction sequencing around 1988 Ogden</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>lineal</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>9800</v>
+      </c>
+      <c r="G76" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="I76" s="13" t="n">
+        <v>10095.52</v>
       </c>
       <c r="J76" s="11" t="inlineStr">
         <is>
-          <t>A-1.0 general notes</t>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 04</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Hot rubber roof membrane lapped into drain sumps, 10"x10"x3/4" recess formed in slab</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>780</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>4680</v>
+      </c>
+      <c r="G77" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>147.76</v>
+      </c>
+      <c r="I77" s="13" t="n">
+        <v>4827.76</v>
+      </c>
+      <c r="J77" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 details 02, 03</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Seal all slab penetrations</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G78" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="I78" s="13" t="n">
+        <v>3695.52</v>
+      </c>
+      <c r="J78" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>A-6.0 detail 01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="n"/>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 7 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n"/>
+      <c r="D79" s="16" t="n"/>
+      <c r="E79" s="16" t="n"/>
+      <c r="F79" s="18" t="n">
+        <v>149706.8</v>
+      </c>
+      <c r="G79" s="16" t="n"/>
+      <c r="H79" s="18" t="n">
+        <v>2142.52</v>
+      </c>
+      <c r="I79" s="18" t="n">
+        <v>151849.32</v>
+      </c>
+      <c r="J79" s="16" t="n"/>
+      <c r="K79" s="16" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 9 - FINISHES</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>Repair of interior finishes damaged by pre-existing water ingress</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="11" t="n"/>
+      <c r="I82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 9 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n"/>
+      <c r="D83" s="16" t="n"/>
+      <c r="E83" s="16" t="n"/>
+      <c r="F83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="16" t="n"/>
+      <c r="H83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="16" t="n"/>
+      <c r="K83" s="16" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 10 - SPECIALTIES</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>REPURPOSED CODE — Firestopping. New 2hr F/T rated firestopping at parkade ceiling where existing products cannot practically be retained. P.C.</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>P.C.</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G86" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>591.04</v>
+      </c>
+      <c r="I86" s="13" t="n">
+        <v>16591.04</v>
+      </c>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 code summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="n"/>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 10 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="n"/>
+      <c r="D87" s="16" t="n"/>
+      <c r="E87" s="16" t="n"/>
+      <c r="F87" s="18" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="18" t="n">
+        <v>591.04</v>
+      </c>
+      <c r="I87" s="18" t="n">
+        <v>16591.04</v>
+      </c>
+      <c r="J87" s="16" t="n"/>
+      <c r="K87" s="16" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>DIVISION 15 - MECHANICAL</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="10" t="n"/>
+      <c r="K89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>Bi-level area drains c/w adjustable grate flush with pavers, and deck drains — NO MECHANICAL DRAWINGS IN THIS SET; A-6.1 refers to mech for all drains. Count assumed</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>909.5</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>5457</v>
+      </c>
+      <c r="G90" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>443.28</v>
+      </c>
+      <c r="I90" s="13" t="n">
+        <v>5900.28</v>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>Subtrade</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1 details 02, 03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Tie-in of new deck drains to existing parkade storm drainage — no as-built information available. P.C.</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>P.C.</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G91" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="I91" s="13" t="n">
+        <v>8795.52</v>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>P.C. allowance</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>A-6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>Sprinkler system modifications — A-1.0 refers to separate sprinkler drawings for 1988 Ogden, not issued</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>NOT INCLUDED</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="11" t="n"/>
+      <c r="I92" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>A-1.0 general notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
           <t>15.8</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>Parkade fan vent remediation — remove accumulated debris within vent, expose drain, add debris shroud, confirm drain functioning</t>
         </is>
       </c>
-      <c r="C77" s="11" t="n">
+      <c r="C93" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D77" s="11" t="inlineStr">
+      <c r="D93" s="11" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="E93" s="12" t="n">
         <v>3850</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="F93" s="12" t="n">
         <v>3850</v>
       </c>
-      <c r="G77" s="11" t="n">
+      <c r="G93" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="H93" s="12" t="n">
         <v>443.28</v>
       </c>
-      <c r="I77" s="11" t="inlineStr">
+      <c r="I93" s="13" t="n">
+        <v>4293.28</v>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
         <is>
           <t>Subtrade</t>
         </is>
       </c>
-      <c r="J77" s="11" t="inlineStr">
+      <c r="K93" s="11" t="inlineStr">
         <is>
           <t>A-1.0 / A-2.1</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="16" t="n"/>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 15 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="n"/>
+      <c r="D94" s="16" t="n"/>
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="18" t="n">
+        <v>17807</v>
+      </c>
+      <c r="G94" s="16" t="n"/>
+      <c r="H94" s="18" t="n">
+        <v>1182.08</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>18989.08</v>
+      </c>
+      <c r="J94" s="16" t="n"/>
+      <c r="K94" s="16" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>DIVISION 16 - ELECTRICAL</t>
         </is>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>16.1</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>Electrical work, landscape and security lighting, and relocation of any conduit encountered in the deck</t>
         </is>
       </c>
-      <c r="C79" s="11" t="n"/>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="13" t="inlineStr">
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>NOT INCLUDED</t>
         </is>
       </c>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="11" t="n"/>
-      <c r="I79" s="11" t="inlineStr">
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="11" t="n"/>
+      <c r="I97" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="K97" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="n"/>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>DIVISION 16 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="n"/>
+      <c r="D98" s="16" t="n"/>
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="16" t="n"/>
+      <c r="K98" s="16" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>TRADE COST — ALL DIVISIONS</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="n"/>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="21" t="n">
+        <v>520336.95</v>
+      </c>
+      <c r="G100" s="19" t="n"/>
+      <c r="H100" s="21" t="n">
+        <v>88286.59999999999</v>
+      </c>
+      <c r="I100" s="21" t="n">
+        <v>608623.55</v>
+      </c>
+      <c r="J100" s="19" t="n"/>
+      <c r="K100" s="19" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3434,7 +3899,7 @@
           <t>1.</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Exposed parkade deck requiring membrane replacement taken at 3,400 sq.ft. This is INFERRED, not stated. It is derived two ways that converge: (a) parkade gross deck of approx. 4,400 sq.ft. less approx. 800 sq.ft. under 1988 Ogden, giving 3,600 sq.ft.; (b) site area 8,315 sq.ft. less building footprints of 3,246 sq.ft. less front and rear yards outside the parkade of approx. 1,843 sq.ft., giving 3,226 sq.ft. The drawings state only the parkade INTERIOR parking area (approx. 4,207 sq.ft., A-2.0). This single quantity drives roughly 45% of the estimate — see Question 1.</t>
         </is>
@@ -3446,7 +3911,7 @@
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Building footprints computed from the dimension strings on A-2.1: 1988 Ogden 32'-9" x 24'-3 3/8" = 795 sq.ft.; 1998 Ogden 32'-3 5/8" x 24'-9 1/4" = 800 sq.ft.; 1066/1068 Maple 45'-4 7/8" x 36'-4 1/4" = 1,651 sq.ft. These reconcile to the stated site dimensions of 129.95 ft and 122.02 ft to within 0.1%.</t>
         </is>
@@ -3458,7 +3923,7 @@
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Membrane upturn taken at 500 lineal ft of deck perimeter x 1.5 ft height (min 8" above finished grade per all A-6.0 details), giving 750 sq.ft. added to the deck area. 10% waste applied to the membrane and drain mat quantities.</t>
         </is>
@@ -3470,7 +3935,7 @@
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Programme assumed at 5 months (11 bi-weekly periods), phased to follow the two-phase tree protection fencing sequence on A-1.0 and the temporary night-seal sequencing on A-6.0 detail 04. Div 1 scales with this duration — if the programme moves, Div 1 and the blended labour rate must both be recomputed.</t>
         </is>
@@ -3482,7 +3947,7 @@
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Contractor's labour is estimated at a blended crew rate and billed at the individual trade rates. Supervisory and labourer lines are carried at their own rates rather than the blend.</t>
         </is>
@@ -3494,7 +3959,7 @@
           <t>6.</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Priced on a 2026 basis. BC PST and material handling are embedded in the rates, which is why no PST line appears in the summary. GST is shown separately.</t>
         </is>
@@ -3506,7 +3971,7 @@
           <t>7.</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Existing structural slab assumed sound and capable of receiving the new topping without structural repair. Only surface concrete remediation of slab, curbs and parkade wall is carried (code 3.4).</t>
         </is>
@@ -3518,7 +3983,7 @@
           <t>8.</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Existing slab assumed to have some fall to drain. Every A-6.0 detail carries the note 'CONTRACTOR TO CONFIRM IF EXISTING IS SLOPED'; topping priced at an average 2" thickness on that basis.</t>
         </is>
@@ -3530,7 +3995,7 @@
           <t>9.</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Parkade assumed to remain in operation, with the deck remediated in phases so that resident vehicle and pedestrian access is maintained throughout. Pricing includes phased night seals but not full parkade closure or off-site parking.</t>
         </is>
@@ -3542,7 +4007,7 @@
           <t>10.</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Existing membrane and drain mat assumed present and lapped to, per A-6.0 detail 05. Not assumed to be reusable anywhere within the scope line.</t>
         </is>
@@ -3554,7 +4019,7 @@
           <t>11.</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Drain count assumed at 6. No mechanical drawings were issued; A-6.1 refers all drain specification to mech.</t>
         </is>
@@ -3566,7 +4031,7 @@
           <t>12.</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Six existing gates, hedges, shrubs and all 18 trees other than the noted section of hedge #9 are retained and protected in place.</t>
         </is>
@@ -3578,7 +4043,7 @@
           <t>13.</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Cost code 10.1 has been repurposed for this job as 'Firestopping' — there is no standing code for 2hr F/T rated fire separation work. This renaming is recorded so the client document and the Sage export agree.</t>
         </is>
@@ -3615,7 +4080,7 @@
           <t>1.</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Building permit and City fees — permit DB-2022-05336 was issued to the Owner in March 2023</t>
         </is>
@@ -3627,7 +4092,7 @@
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Structural engineering design, review of deteriorated studs, and field review</t>
         </is>
@@ -3639,7 +4104,7 @@
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Arborist report, tree removal permits and landscape plan approval</t>
         </is>
@@ -3651,7 +4116,7 @@
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Landscape and mechanical consultant design — neither drawing package was issued with this set</t>
         </is>
@@ -3663,7 +4128,7 @@
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Strata legal, engineering review and depreciation report costs</t>
         </is>
@@ -3675,7 +4140,7 @@
           <t>6.</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Temporary relocation of residents and off-site parking during the works</t>
         </is>
@@ -3687,7 +4152,7 @@
           <t>7.</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Hazardous materials survey and abatement</t>
         </is>
@@ -3699,7 +4164,7 @@
           <t>8.</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Insulation, vapour barrier, concrete topping, gypsum board and interior finish at the base of exterior walls — noted on A-6.0 as by the interior renovation contractor</t>
         </is>
@@ -3711,7 +4176,7 @@
           <t>9.</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Structural repair to parkade slab, columns, beams or walls beyond surface concrete remediation</t>
         </is>
@@ -3723,7 +4188,7 @@
           <t>10.</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Repair of interior finishes damaged by pre-existing water ingress</t>
         </is>
@@ -3735,7 +4200,7 @@
           <t>11.</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Sprinkler system modifications</t>
         </is>
@@ -3747,7 +4212,7 @@
           <t>12.</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Electrical work, landscape and security lighting, and relocation of conduit encountered in the deck</t>
         </is>
@@ -3759,7 +4224,7 @@
           <t>13.</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Reconstruction of the concrete driveway ramp surface</t>
         </is>
@@ -3771,7 +4236,7 @@
           <t>14.</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Any upgrade of parkade items to current code</t>
         </is>
@@ -3808,7 +4273,7 @@
           <t>1.</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>What is the actual area of exposed parkade deck within the scope-of-slab-remediation line on A-2.1? The drawings state the parkade INTERIOR parking area (approx. 4,207 sq.ft.) but never the deck area to be remediated, and the three nested lines on A-2.1 (scope line, exterior face of parkade, interior face of parkade) are within a foot or two of each other at the only point they are labelled. A confirmed deck area, or permission to survey the site, is the single highest-value piece of information for this estimate.
 Assumed meanwhile: 3,400 sq.ft. of exposed deck. Every 100 sq.ft. of error moves the estimate by approximately $3,900 before fee and GST.
@@ -3822,7 +4287,7 @@
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Is DB-2022-05336 rev 04 dated 23.03.06 still the current set? The permit was accepted by the City on 2023-03-22, over three years ago. Has the set been revised, has the permit lapsed or been extended, and has any of the work already been carried out?
 Assumed meanwhile: Priced as the March 2023 issue, with rates escalated to a 2026 construction start.
@@ -3836,7 +4301,7 @@
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Where are the landscape drawings? A-6.0 and A-6.1 refer to landscape for finishes at eight separate points, and A-2.1 shows pavers on pedestals, pavers on gravel, lawn, planting and a BBQ area without specification.
 Assumed meanwhile: P.C. allowances of $18,000 for planting and $12,000 for hard landscaping, plus unit-rate paving at mid-range paver specifications.
@@ -3850,7 +4315,7 @@
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Where are the structural drawings? A-6.0 says 'SEE STRUCTURAL FOR STEEL REINFORCEMENT' and 'STUDS TO BE REVIEWED BY STRUCTURAL', and A-6.1 says 'NEW REINFORCING PER STRUCTURAL'.
 Assumed meanwhile: P.C. of $9,500 for reinforcing and $14,000 for deteriorated sheathing and stud replacement.
@@ -3864,7 +4329,7 @@
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Where are the mechanical drawings? A-6.1 refers all deck drains, area drains and drain insulation to mech, and gives no count or location.
 Assumed meanwhile: 6 drains, tied into existing parkade storm drainage under a $8,500 P.C.
@@ -3878,7 +4343,7 @@
           <t>6.</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Is the existing slab sloped to drain? Six separate details carry the note 'CONTRACTOR TO CONFIRM IF EXISTING IS SLOPED'. If it is flat, the topping must build the entire 2% fall and thickness increases substantially at the high points.
 Assumed meanwhile: Existing slab has partial fall; topping priced at 2" average.
@@ -3892,7 +4357,7 @@
           <t>7.</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>What is the condition of the existing concrete slab, curbs and parkade wall beneath the topping? None of it is visible and no condition survey or engineering report accompanies the set.
 Assumed meanwhile: P.C. of $32,000, sized at surface repair to 15% of the deck area.
@@ -3906,7 +4371,7 @@
           <t>8.</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Must the parkade remain in use throughout, and must all four units retain vehicle access at all times? This governs the phasing and therefore the programme.
 Assumed meanwhile: Parkade remains in operation; work phased with night seals; 5-month programme.
@@ -3920,7 +4385,7 @@
           <t>9.</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Has a hazardous materials survey been done? The buildings date from 1990, which is within the range for asbestos in below-grade waterproofing and mastics. The existing membrane will be removed and disposed of.
 Assumed meanwhile: No hazardous material present. Survey and abatement excluded.
@@ -3934,7 +4399,7 @@
           <t>10.</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>How much fill sits above the parkade slab? Depth is not dimensioned anywhere in the set and drives both the excavation quantity and the disposal load count.
 Assumed meanwhile: 8" average fill plus 3" topping, giving 125 cubic yards and 14 bins.
@@ -3948,7 +4413,7 @@
           <t>11.</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Confirm the extent of the 2hr F/T firestopping at the parkade ceiling. A-1.0 says new firestopping will be installed 'where it is impractical to keep existing fire stopping products' — that condition cannot be assessed until the deck is opened.
 Assumed meanwhile: P.C. of $16,000.
@@ -3962,7 +4427,7 @@
           <t>12.</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Caisley completed an interior renovation at 1988 Ogden Ave. Is that the same unit referenced on A-6.0 as having interior work by others, and does any of that work interface with this scope?
 Assumed meanwhile: The interior scope at the base of exterior walls is by the interior renovation contractor and is excluded here.
@@ -4001,7 +4466,7 @@
           <t>1.</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Concrete remediation of the slab, curbs and parkade wall (3.4) — Priced at $32,000 against a completely unseen substrate. This is the classic parkade remediation exposure: the extent of delamination, spalling and rebar corrosion is unknowable until the topping comes off, and by then the contract is signed and the deck is open. On a 1990 slab that has been leaking badly enough to justify a full membrane replacement, finding two to three times this allowance would not be unusual. Recommend this line be carried as a unit-rate provisional item with an agreed $/sq.ft. repair rate rather than a lump sum, so the exposure is priced rather than argued.</t>
         </is>
@@ -4013,7 +4478,7 @@
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Deck area (2.2, 3.2, 7.1, 7.6) — The estimate rests on an inferred 3,400 sq.ft. that the drawings never state. Roughly 45% of the trade cost moves directly with it. A site survey before contract would remove more risk per dollar than anything else available here.</t>
         </is>
@@ -4025,7 +4490,7 @@
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Existing slab fall (3.2) — Six details ask the contractor to confirm whether the existing slab is sloped, which means the architect does not know. If it is flat, the topping must generate the full 2% fall and both volume and pumping cost rise sharply. Toppings are also the line most likely to trigger a knock-on to door sills, thresholds and the three 39.5 door sills surveyed on A-1.0 and A-2.0.</t>
         </is>
@@ -4037,7 +4502,7 @@
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>The three missing consultant packages (2.11, 2.16, 3.3, 6.2, 15.1) — Landscape, structural and mechanical are all referred to and none are issued. Approximately $98,000 of this estimate sits in P.C. allowances covering scope that has not been designed. This is precisely the condition that produced the Ogden overrun: 68 change orders against scope that did not exist at estimate time. The estimate should not be presented as a fixed price against an undesigned scope.</t>
         </is>
@@ -4049,7 +4514,7 @@
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Age of the drawing set — The set is over three years old and the permit was accepted in March 2023. Vancouver building permits generally lapse if work does not commence within two years. If the permit has lapsed, re-application may attract current code requirements and the mobilization assumptions change.</t>
         </is>
@@ -4061,7 +4526,7 @@
           <t>6.</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Occupied site and phasing (1.1, 1.8, 7.6) — Four occupied townhouses, a live parkade, 18 retained trees with mandatory arborist supervision inside the protection zones, and a membrane that cannot be left open overnight. Every one of those constrains sequencing. The 5-month programme assumes phasing works as drawn on A-6.0 detail 04; if the strata requires narrower work windows or continuous parkade access, duration extends and Div 1 goes with it.</t>
         </is>
@@ -4073,7 +4538,7 @@
           <t>7.</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Hazardous materials (2.2, 2.3) — A 1990 building, an existing below-grade waterproofing membrane being removed wholesale, and no survey in the set. Discovery mid-demolition stops the job and the abatement is not in this number.</t>
         </is>
@@ -4085,7 +4550,7 @@
           <t>8.</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Tree protection (1.2, 2.3) — The City has accepted a tree plan retaining 18 trees and hedges, and A-1.0 requires certified arborist supervision for any excavation encroaching a protection zone. Excavation to expose the top of the parkade wall runs directly along the paths where those trees sit. Root conflict is likely and the remedies — hand digging, root pruning, or a redesigned edge detail — are all slower than the rate assumes.</t>
         </is>
